--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_171_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_171_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>3</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>81</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>23</v>
@@ -4292,10 +4292,10 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4880,16 +4880,16 @@
         <v>21</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>5</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
         <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
         <v>2</v>
@@ -6059,13 +6059,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>7</v>
@@ -6252,7 +6252,7 @@
         <v>12</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -6448,7 +6448,7 @@
         <v>5</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>93</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>29</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_171_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_171_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
         <v>6</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>2</v>
       </c>
       <c r="X30" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -4892,14 +4892,14 @@
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5676,14 +5676,14 @@
         <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6460,10 +6460,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="Y48" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="AA48" t="n">
